--- a/Tagihan/2026/Juli/SMA Tanta.xlsx
+++ b/Tagihan/2026/Juli/SMA Tanta.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Data Pekerjaan\Tagihan\2026\Juli\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{FC15C5EB-11B4-45E4-A290-B7E5B7D44A9C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{84BF3676-221C-441B-9710-E81B6B0D7454}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="19095" yWindow="0" windowWidth="19410" windowHeight="15585" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2730" yWindow="720" windowWidth="19410" windowHeight="15480" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="23">
   <si>
     <t>NO.</t>
   </si>
@@ -149,6 +149,9 @@
   </si>
   <si>
     <t>Lot</t>
+  </si>
+  <si>
+    <t>MCB 6A</t>
   </si>
 </sst>
 </file>
@@ -245,7 +248,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="20">
+  <borders count="21">
     <border>
       <left/>
       <right/>
@@ -476,11 +479,22 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="52">
+  <cellXfs count="54">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -616,6 +630,12 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -689,13 +709,13 @@
     <xdr:from>
       <xdr:col>2</xdr:col>
       <xdr:colOff>154781</xdr:colOff>
-      <xdr:row>31</xdr:row>
+      <xdr:row>30</xdr:row>
       <xdr:rowOff>23812</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
       <xdr:colOff>2320131</xdr:colOff>
-      <xdr:row>38</xdr:row>
+      <xdr:row>37</xdr:row>
       <xdr:rowOff>79851</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -1030,7 +1050,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="B5:N39"/>
+  <dimension ref="B5:N38"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="2.28515625" customWidth="1"/>
@@ -1160,39 +1180,49 @@
       </c>
     </row>
     <row r="18" spans="2:7" s="6" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B18" s="2">
+      <c r="B18" s="12">
         <v>2</v>
       </c>
-      <c r="C18" s="33" t="s">
+      <c r="C18" s="52" t="s">
+        <v>22</v>
+      </c>
+      <c r="D18" s="53">
+        <v>1</v>
+      </c>
+      <c r="E18" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="F18" s="27">
+        <v>45000</v>
+      </c>
+      <c r="G18" s="28"/>
+    </row>
+    <row r="19" spans="2:7" s="6" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B19" s="2">
+        <v>2</v>
+      </c>
+      <c r="C19" s="33" t="s">
         <v>20</v>
       </c>
-      <c r="D18" s="2">
+      <c r="D19" s="2">
         <v>1</v>
       </c>
-      <c r="E18" s="12" t="s">
+      <c r="E19" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="F18" s="29">
-        <v>150000</v>
-      </c>
-      <c r="G18" s="28">
-        <f>D18*F18</f>
-        <v>150000</v>
-      </c>
-    </row>
-    <row r="19" spans="2:7" s="6" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B19" s="2"/>
-      <c r="C19" s="33"/>
-      <c r="D19" s="2"/>
-      <c r="E19" s="12"/>
-      <c r="F19" s="29"/>
-      <c r="G19" s="28"/>
+      <c r="F19" s="29">
+        <v>200000</v>
+      </c>
+      <c r="G19" s="28">
+        <f>D19*F19</f>
+        <v>200000</v>
+      </c>
     </row>
     <row r="20" spans="2:7" s="6" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B20" s="2"/>
       <c r="C20" s="33"/>
       <c r="D20" s="2"/>
-      <c r="E20" s="12"/>
+      <c r="E20" s="2"/>
       <c r="F20" s="29"/>
       <c r="G20" s="28"/>
     </row>
@@ -1206,10 +1236,10 @@
     </row>
     <row r="22" spans="2:7" s="6" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B22" s="2"/>
-      <c r="C22" s="33"/>
-      <c r="D22" s="2"/>
-      <c r="E22" s="2"/>
-      <c r="F22" s="29"/>
+      <c r="C22" s="34"/>
+      <c r="D22" s="5"/>
+      <c r="E22" s="5"/>
+      <c r="F22" s="30"/>
       <c r="G22" s="28"/>
     </row>
     <row r="23" spans="2:7" s="6" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -1237,7 +1267,7 @@
       <c r="G25" s="28"/>
     </row>
     <row r="26" spans="2:7" s="6" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B26" s="2"/>
+      <c r="B26" s="5"/>
       <c r="C26" s="34"/>
       <c r="D26" s="5"/>
       <c r="E26" s="5"/>
@@ -1252,97 +1282,89 @@
       <c r="F27" s="30"/>
       <c r="G27" s="28"/>
     </row>
-    <row r="28" spans="2:7" s="6" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="2:7" s="6" customFormat="1" ht="20.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B28" s="5"/>
-      <c r="C28" s="34"/>
+      <c r="C28" s="5"/>
       <c r="D28" s="5"/>
       <c r="E28" s="5"/>
       <c r="F28" s="30"/>
-      <c r="G28" s="28"/>
-    </row>
-    <row r="29" spans="2:7" s="6" customFormat="1" ht="20.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B29" s="5"/>
-      <c r="C29" s="5"/>
-      <c r="D29" s="5"/>
-      <c r="E29" s="5"/>
-      <c r="F29" s="30"/>
-      <c r="G29" s="30"/>
-    </row>
-    <row r="30" spans="2:7" ht="20.25" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B30" s="44" t="s">
+      <c r="G28" s="30"/>
+    </row>
+    <row r="29" spans="2:7" ht="20.25" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B29" s="44" t="s">
         <v>4</v>
       </c>
-      <c r="C30" s="45"/>
-      <c r="D30" s="45"/>
-      <c r="E30" s="45"/>
-      <c r="F30" s="46"/>
-      <c r="G30" s="31">
-        <f>SUM(G17:G29)</f>
-        <v>400000</v>
-      </c>
-    </row>
-    <row r="31" spans="2:7" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="B31" s="3"/>
-      <c r="C31" s="3"/>
-      <c r="D31" s="3"/>
-      <c r="E31" s="3"/>
-      <c r="F31" s="20"/>
-      <c r="G31" s="21"/>
-    </row>
-    <row r="33" spans="2:8" s="23" customFormat="1" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="B33" s="47" t="s">
+      <c r="C29" s="45"/>
+      <c r="D29" s="45"/>
+      <c r="E29" s="45"/>
+      <c r="F29" s="46"/>
+      <c r="G29" s="31">
+        <f>SUM(G17:G28)</f>
+        <v>450000</v>
+      </c>
+    </row>
+    <row r="30" spans="2:7" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
+      <c r="B30" s="3"/>
+      <c r="C30" s="3"/>
+      <c r="D30" s="3"/>
+      <c r="E30" s="3"/>
+      <c r="F30" s="20"/>
+      <c r="G30" s="21"/>
+    </row>
+    <row r="32" spans="2:7" s="23" customFormat="1" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="B32" s="47" t="s">
         <v>5</v>
       </c>
-      <c r="C33" s="47"/>
-      <c r="D33" s="22"/>
-      <c r="E33" s="22"/>
-      <c r="F33" s="48" t="s">
+      <c r="C32" s="47"/>
+      <c r="D32" s="22"/>
+      <c r="E32" s="22"/>
+      <c r="F32" s="48" t="s">
         <v>6</v>
       </c>
-      <c r="G33" s="48"/>
-    </row>
-    <row r="37" spans="2:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B37" s="38"/>
-      <c r="C37" s="38"/>
-      <c r="D37" s="38"/>
-      <c r="E37" s="38"/>
-      <c r="F37" s="38"/>
-      <c r="G37" s="38"/>
+      <c r="G32" s="48"/>
+    </row>
+    <row r="36" spans="2:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B36" s="38"/>
+      <c r="C36" s="38"/>
+      <c r="D36" s="38"/>
+      <c r="E36" s="38"/>
+      <c r="F36" s="38"/>
+      <c r="G36" s="38"/>
+    </row>
+    <row r="37" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B37" s="42" t="s">
+        <v>14</v>
+      </c>
+      <c r="C37" s="43"/>
+      <c r="D37" s="43"/>
+      <c r="E37" s="43"/>
+      <c r="F37" s="24"/>
+      <c r="G37" s="26"/>
+      <c r="H37" s="25"/>
     </row>
     <row r="38" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B38" s="42" t="s">
-        <v>14</v>
-      </c>
-      <c r="C38" s="43"/>
-      <c r="D38" s="43"/>
-      <c r="E38" s="43"/>
-      <c r="F38" s="24"/>
-      <c r="G38" s="26"/>
+      <c r="B38" s="39" t="s">
+        <v>15</v>
+      </c>
+      <c r="C38" s="40"/>
+      <c r="D38" s="40"/>
+      <c r="E38" s="40"/>
+      <c r="F38" s="40"/>
+      <c r="G38" s="40"/>
       <c r="H38" s="25"/>
-    </row>
-    <row r="39" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B39" s="39" t="s">
-        <v>15</v>
-      </c>
-      <c r="C39" s="40"/>
-      <c r="D39" s="40"/>
-      <c r="E39" s="40"/>
-      <c r="F39" s="40"/>
-      <c r="G39" s="40"/>
-      <c r="H39" s="25"/>
     </row>
   </sheetData>
   <mergeCells count="13">
     <mergeCell ref="C7:G8"/>
     <mergeCell ref="C9:G9"/>
     <mergeCell ref="C10:G10"/>
-    <mergeCell ref="B37:G37"/>
-    <mergeCell ref="B39:G39"/>
+    <mergeCell ref="B36:G36"/>
+    <mergeCell ref="B38:G38"/>
     <mergeCell ref="C11:G11"/>
-    <mergeCell ref="B38:E38"/>
-    <mergeCell ref="B30:F30"/>
-    <mergeCell ref="B33:C33"/>
-    <mergeCell ref="F33:G33"/>
+    <mergeCell ref="B37:E37"/>
+    <mergeCell ref="B29:F29"/>
+    <mergeCell ref="B32:C32"/>
+    <mergeCell ref="F32:G32"/>
     <mergeCell ref="F13:G13"/>
     <mergeCell ref="F14:G14"/>
     <mergeCell ref="B14:C14"/>
